--- a/data/trans_dic/P24D-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P24D-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha intentado dejar de fumar alguna vez</t>
+          <t>Población que ha intentado dejar de fumar alguna vez (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,96; 38,51</t>
+          <t>27,95; 38,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,54; 50,51</t>
+          <t>40,01; 51,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,21; 48,08</t>
+          <t>34,72; 48,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,34; 42,43</t>
+          <t>26,67; 42,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,47; 38,81</t>
+          <t>24,6; 38,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,44; 57,89</t>
+          <t>43,02; 57,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,19; 53,02</t>
+          <t>35,89; 52,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43,12; 60,26</t>
+          <t>42,62; 60,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,57; 36,58</t>
+          <t>28,1; 36,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42,54; 51,88</t>
+          <t>42,48; 51,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37,85; 48,17</t>
+          <t>37,82; 47,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,25; 46,96</t>
+          <t>34,26; 46,39</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,93; 31,75</t>
+          <t>25,25; 31,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,82; 49,87</t>
+          <t>42,83; 50,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,26; 46,54</t>
+          <t>38,99; 46,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29,05; 37,9</t>
+          <t>28,9; 37,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,96; 39,33</t>
+          <t>30,99; 39,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,35; 54,73</t>
+          <t>46,43; 54,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,17; 48,44</t>
+          <t>41,12; 48,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,15; 47,24</t>
+          <t>39,27; 48,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,61; 33,57</t>
+          <t>28,66; 33,68</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,61; 51,18</t>
+          <t>45,81; 51,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41,18; 46,35</t>
+          <t>41,13; 46,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,65; 40,9</t>
+          <t>34,68; 41,08</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,74; 42,14</t>
+          <t>27,54; 41,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,79; 56,53</t>
+          <t>38,85; 56,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,05; 55,48</t>
+          <t>38,09; 56,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,27; 61,75</t>
+          <t>35,93; 62,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,46; 46,78</t>
+          <t>30,29; 47,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,04; 63,82</t>
+          <t>46,08; 63,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,68; 52,32</t>
+          <t>33,79; 51,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,76; 47,65</t>
+          <t>30,34; 48,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,79; 41,21</t>
+          <t>30,41; 41,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,04; 57,35</t>
+          <t>45,19; 56,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37,84; 50,66</t>
+          <t>37,89; 50,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35,47; 51,96</t>
+          <t>35,42; 51,94</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,83; 32,93</t>
+          <t>28,05; 33,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,45; 49,29</t>
+          <t>43,63; 48,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,0; 46,0</t>
+          <t>39,89; 45,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,18; 39,39</t>
+          <t>31,55; 39,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,9; 38,21</t>
+          <t>31,47; 37,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,22; 54,72</t>
+          <t>47,87; 54,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,18; 47,78</t>
+          <t>40,93; 47,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,05; 47,0</t>
+          <t>39,97; 47,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,06; 34,34</t>
+          <t>30,02; 33,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46,24; 50,45</t>
+          <t>46,13; 50,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41,22; 45,86</t>
+          <t>41,29; 45,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,21; 41,83</t>
+          <t>36,32; 41,67</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha intentado dejar de fumar alguna vez</t>
+          <t>Población que ha intentado dejar de fumar alguna vez (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>104458; 143864</t>
+          <t>104429; 142148</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>132456; 169200</t>
+          <t>134023; 171641</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79018; 107888</t>
+          <t>77905; 108706</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38589; 59898</t>
+          <t>37657; 60377</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>43199; 68509</t>
+          <t>43432; 68207</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86901; 115793</t>
+          <t>86062; 115787</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>49301; 72221</t>
+          <t>48890; 71819</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33714; 47117</t>
+          <t>33325; 46991</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>157202; 201278</t>
+          <t>154593; 198159</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>227623; 277581</t>
+          <t>227284; 274561</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136508; 173713</t>
+          <t>136386; 172533</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>77322; 103020</t>
+          <t>75150; 101761</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>203648; 259317</t>
+          <t>206238; 258282</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>364730; 424796</t>
+          <t>364807; 427378</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>315992; 374580</t>
+          <t>313874; 370473</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>168931; 220393</t>
+          <t>168054; 218159</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>166941; 212055</t>
+          <t>167122; 212897</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>292708; 345624</t>
+          <t>293238; 345032</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>272132; 320161</t>
+          <t>271808; 321616</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>180199; 217437</t>
+          <t>180730; 220998</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>387937; 455208</t>
+          <t>388643; 456777</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>676549; 759121</t>
+          <t>679597; 759598</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>603613; 679431</t>
+          <t>602901; 680917</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>360945; 426154</t>
+          <t>361282; 427990</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>52803; 80217</t>
+          <t>52424; 79163</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64233; 91264</t>
+          <t>62712; 91672</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51812; 75545</t>
+          <t>51859; 76653</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36482; 63872</t>
+          <t>37165; 65062</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42263; 64903</t>
+          <t>42022; 65719</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63366; 87834</t>
+          <t>63422; 86973</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40570; 63015</t>
+          <t>40697; 62542</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31770; 50866</t>
+          <t>32387; 51347</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>101327; 135632</t>
+          <t>100075; 136331</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>134687; 171498</t>
+          <t>135142; 170247</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>97102; 129990</t>
+          <t>97219; 130647</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74558; 109207</t>
+          <t>74445; 109161</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>384310; 454734</t>
+          <t>387290; 456308</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>585836; 664504</t>
+          <t>588193; 658233</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>466165; 536152</t>
+          <t>464930; 535211</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>257635; 325470</t>
+          <t>260682; 325433</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>272592; 326520</t>
+          <t>268931; 323551</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>467390; 530327</t>
+          <t>463910; 527689</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>377911; 438411</t>
+          <t>375578; 436598</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>258378; 303260</t>
+          <t>257873; 303650</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>671967; 767700</t>
+          <t>671062; 759321</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1071491; 1169276</t>
+          <t>1069082; 1167296</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>858750; 955342</t>
+          <t>860022; 953638</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>532738; 615432</t>
+          <t>534365; 613185</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P24D-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P24D-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,95; 38,05</t>
+          <t>28,29; 37,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,01; 51,24</t>
+          <t>39,81; 50,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,72; 48,44</t>
+          <t>35,29; 48,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,67; 42,77</t>
+          <t>26,86; 42,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,6; 38,64</t>
+          <t>24,84; 39,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,02; 57,88</t>
+          <t>43,09; 58,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,89; 52,72</t>
+          <t>36,33; 53,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,62; 60,1</t>
+          <t>44,06; 61,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,1; 36,02</t>
+          <t>28,74; 36,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42,48; 51,32</t>
+          <t>42,84; 51,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37,82; 47,84</t>
+          <t>37,43; 48,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,26; 46,39</t>
+          <t>34,72; 47,19</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,25; 31,62</t>
+          <t>25,34; 31,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,83; 50,17</t>
+          <t>42,51; 49,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,99; 46,03</t>
+          <t>39,09; 46,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,9; 37,51</t>
+          <t>30,2; 39,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,99; 39,48</t>
+          <t>31,02; 38,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,43; 54,63</t>
+          <t>46,88; 54,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,12; 48,66</t>
+          <t>40,88; 48,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>39,27; 48,02</t>
+          <t>38,96; 47,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,66; 33,68</t>
+          <t>28,56; 33,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45,81; 51,21</t>
+          <t>45,77; 50,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41,13; 46,45</t>
+          <t>40,96; 46,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,68; 41,08</t>
+          <t>35,48; 41,35</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>44,58%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>41,94%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,54; 41,58</t>
+          <t>27,88; 41,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,85; 56,79</t>
+          <t>39,97; 56,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,09; 56,3</t>
+          <t>37,18; 55,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35,93; 62,9</t>
+          <t>35,26; 55,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,29; 47,37</t>
+          <t>29,86; 46,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,08; 63,19</t>
+          <t>46,56; 63,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,79; 51,92</t>
+          <t>33,64; 51,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>30,34; 48,1</t>
+          <t>31,47; 48,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,41; 41,43</t>
+          <t>30,97; 41,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45,19; 56,93</t>
+          <t>44,68; 57,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37,89; 50,91</t>
+          <t>38,35; 51,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>35,42; 51,94</t>
+          <t>35,77; 48,55</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>39,26%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,05; 33,05</t>
+          <t>28,03; 33,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,63; 48,82</t>
+          <t>43,19; 49,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,89; 45,92</t>
+          <t>40,2; 46,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,55; 39,39</t>
+          <t>32,18; 39,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,47; 37,87</t>
+          <t>31,4; 37,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,87; 54,45</t>
+          <t>47,64; 54,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,93; 47,58</t>
+          <t>41,48; 47,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,97; 47,06</t>
+          <t>40,59; 47,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,02; 33,97</t>
+          <t>30,15; 34,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46,13; 50,37</t>
+          <t>46,17; 50,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41,29; 45,78</t>
+          <t>41,24; 45,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,32; 41,67</t>
+          <t>36,82; 41,78</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48689</t>
+          <t>51433</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>40538</t>
+          <t>45206</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89227</t>
+          <t>96639</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>104429; 142148</t>
+          <t>105698; 140856</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>134023; 171641</t>
+          <t>133373; 170411</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77905; 108706</t>
+          <t>79198; 109364</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>37657; 60377</t>
+          <t>40952; 65171</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>43432; 68207</t>
+          <t>43861; 69188</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86062; 115787</t>
+          <t>86204; 116649</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48890; 71819</t>
+          <t>49480; 73024</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33325; 46991</t>
+          <t>37658; 52449</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>154593; 198159</t>
+          <t>158113; 199756</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>227284; 274561</t>
+          <t>229226; 274561</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136386; 172533</t>
+          <t>134965; 173107</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>75150; 101761</t>
+          <t>82624; 112290</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>193495</t>
+          <t>218566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>199765</t>
+          <t>215078</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>393261</t>
+          <t>433644</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>206238; 258282</t>
+          <t>206982; 260115</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>364807; 427378</t>
+          <t>362143; 422173</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>313874; 370473</t>
+          <t>314602; 373877</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>168054; 218159</t>
+          <t>190567; 246099</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>167122; 212897</t>
+          <t>167253; 210009</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>293238; 345032</t>
+          <t>296083; 346120</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>271808; 321616</t>
+          <t>270216; 323814</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>180730; 220998</t>
+          <t>193773; 235980</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>388643; 456777</t>
+          <t>387302; 458968</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>679597; 759598</t>
+          <t>678956; 754315</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>602901; 680917</t>
+          <t>600416; 679196</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>361282; 427990</t>
+          <t>400377; 466538</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48489</t>
+          <t>49165</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40770</t>
+          <t>46024</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89259</t>
+          <t>95189</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>52424; 79163</t>
+          <t>53077; 79137</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>62712; 91672</t>
+          <t>64529; 90456</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51859; 76653</t>
+          <t>50620; 75415</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37165; 65062</t>
+          <t>38886; 60712</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>42022; 65719</t>
+          <t>41425; 63876</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63422; 86973</t>
+          <t>64074; 87852</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40697; 62542</t>
+          <t>40525; 61908</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32387; 51347</t>
+          <t>36717; 56314</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100075; 136331</t>
+          <t>101925; 136919</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>135142; 170247</t>
+          <t>133610; 170530</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>97219; 130647</t>
+          <t>98406; 131051</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74445; 109161</t>
+          <t>81179; 110188</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>290674</t>
+          <t>319164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>281073</t>
+          <t>306308</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>571747</t>
+          <t>625472</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>387290; 456308</t>
+          <t>387022; 457836</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>588193; 658233</t>
+          <t>582382; 663560</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>464930; 535211</t>
+          <t>468554; 538390</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>260682; 325433</t>
+          <t>287572; 351293</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>268931; 323551</t>
+          <t>268296; 324646</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>463910; 527689</t>
+          <t>461690; 528034</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>375578; 436598</t>
+          <t>380600; 436747</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>257873; 303650</t>
+          <t>283969; 331403</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>671062; 759321</t>
+          <t>673899; 762196</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1069082; 1167296</t>
+          <t>1069989; 1170495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>860022; 953638</t>
+          <t>858998; 955017</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>534365; 613185</t>
+          <t>586559; 665603</t>
         </is>
       </c>
     </row>
